--- a/data/file_generation/reference/data_388/支出金额交叉汇总表_res.xlsx
+++ b/data/file_generation/reference/data_388/支出金额交叉汇总表_res.xlsx
@@ -1,26 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29721"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangxin1/Desktop/datasets/数据分析/output/data_388/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE66DBDD-569D-704C-A6CC-45E01D561978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{DE66DBDD-569D-704C-A6CC-45E01D561978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6200EDEC-3846-4ACA-AB80-9B623607ECAE}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="支出汇总" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>交易日期</t>
   </si>
@@ -28,32 +44,22 @@
     <t>转取</t>
   </si>
   <si>
+    <t>户名_4</t>
+  </si>
+  <si>
     <t>费用外收</t>
   </si>
   <si>
-    <t>万源市力净洗涤服务部</t>
+    <t>户名_5</t>
   </si>
   <si>
-    <t>万源市兴盛源商贸有限公司</t>
+    <t>户名_6</t>
   </si>
   <si>
-    <t>达州市途麦酒店管理有限公司</t>
+    <t>户名_7</t>
   </si>
   <si>
-    <t>2025-09-13</t>
-  </si>
-  <si>
-    <t>2025-09-16</t>
-  </si>
-  <si>
-    <t>2025-09-23</t>
-  </si>
-  <si>
-    <t>王A</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>何B</t>
+    <t>户名_8</t>
   </si>
 </sst>
 </file>
@@ -69,13 +75,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
@@ -85,9 +84,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -98,7 +102,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -121,17 +125,42 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -435,7 +464,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.1"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="6" customWidth="1"/>
@@ -447,117 +476,126 @@
     <col min="8" max="8" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15">
+    <row r="1" spans="1:8" ht="13.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="H1" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="3">
+    <row r="2" spans="1:8" ht="13.5">
+      <c r="A2" s="3">
+        <v>45913</v>
+      </c>
+      <c r="B2" s="4">
         <v>15</v>
       </c>
-      <c r="C2" s="3">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3">
-        <v>0</v>
-      </c>
-      <c r="F2" s="3">
-        <v>0</v>
-      </c>
-      <c r="G2" s="3">
-        <v>0</v>
-      </c>
-      <c r="H2" s="3">
+      <c r="C2" s="4">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+      <c r="H2" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="3">
-        <v>0</v>
-      </c>
-      <c r="C3" s="3">
+    <row r="3" spans="1:8" ht="13.5">
+      <c r="A3" s="3">
+        <v>45916</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0</v>
+      </c>
+      <c r="C3" s="4">
         <v>33651</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="4">
         <v>22.5</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="4">
         <v>11800</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="4">
         <v>1920</v>
       </c>
-      <c r="G3" s="3">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3">
+      <c r="G3" s="4">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="3">
-        <v>0</v>
-      </c>
-      <c r="C4" s="3">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3">
+    <row r="4" spans="1:8" ht="13.5">
+      <c r="A4" s="3">
+        <v>45923</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4">
         <v>18</v>
       </c>
-      <c r="E4" s="3">
-        <v>0</v>
-      </c>
-      <c r="F4" s="3">
-        <v>0</v>
-      </c>
-      <c r="G4" s="3">
+      <c r="E4" s="4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4">
         <v>10750</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="4">
         <v>26000</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文档" ma:contentTypeID="0x01010028C7B6C620067247A35EF62A3E68EE62" ma:contentTypeVersion="2" ma:contentTypeDescription="新建文档。" ma:contentTypeScope="" ma:versionID="afb9c51b290a08b96651a149e23bf63d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5c256d110dbc588a3a1a6b419ffcea87" ns2:_="">
     <xsd:import namespace="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7"/>
@@ -705,15 +743,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -721,11 +750,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22FA4FB2-674E-422F-8E3B-D0F2F98F0227}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06763058-8887-424B-AC0E-5B63E777D2B2}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22FA4FB2-674E-422F-8E3B-D0F2F98F0227}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
